--- a/school_2/floors/PDF/1, 2, 3 Лестницы (НЗ)/ремонта маршей.xlsx
+++ b/school_2/floors/PDF/1, 2, 3 Лестницы (НЗ)/ремонта маршей.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="резка" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
   <si>
     <t>Спецификация выполненных работ</t>
   </si>
@@ -31,63 +31,69 @@
   </si>
   <si>
     <t>Объем</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>Объем, м2</t>
+  </si>
+  <si>
+    <t>Объем, м3</t>
+  </si>
+  <si>
+    <t>Итог:</t>
+  </si>
+  <si>
+    <t>Демонтаж бетона с сохранением арматуры</t>
+  </si>
+  <si>
+    <t>пог. м.</t>
+  </si>
+  <si>
+    <t>Лестницы</t>
+  </si>
+  <si>
+    <t>Объем, п.м.</t>
+  </si>
+  <si>
+    <t>ЛК-1</t>
+  </si>
+  <si>
+    <t>ЛК-2</t>
+  </si>
+  <si>
+    <t>ЛК-3</t>
+  </si>
+  <si>
+    <t>ЛК-4</t>
+  </si>
+  <si>
+    <t>ЛК-5</t>
+  </si>
+  <si>
+    <t>Армировка сеткой 50х50 яч.</t>
+  </si>
+  <si>
+    <t>м2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Алмазная резка железобетонный конструкций </t>
   </si>
   <si>
     <t>Устройство монолитных
 лестничных маршей (Монтаж
 ступеней ремонтным
-составом RC45)</t>
-  </si>
-  <si>
-    <t>м3</t>
-  </si>
-  <si>
-    <t>Тип</t>
-  </si>
-  <si>
-    <t>Объем, м2</t>
-  </si>
-  <si>
-    <t>Объем, м3</t>
-  </si>
-  <si>
-    <t>Итог:</t>
-  </si>
-  <si>
-    <t>Демонтаж бетона с сохранением арматуры</t>
-  </si>
-  <si>
-    <t>Алмазная резка железобетонный конструкций/ 180 мм.</t>
-  </si>
-  <si>
-    <t>пог. м.</t>
-  </si>
-  <si>
-    <t>Лестницы</t>
-  </si>
-  <si>
-    <t>Объем, п.м.</t>
-  </si>
-  <si>
-    <t>ЛК-1</t>
-  </si>
-  <si>
-    <t>ЛК-2</t>
-  </si>
-  <si>
-    <t>ЛК-3</t>
-  </si>
-  <si>
-    <t>ЛК-4</t>
-  </si>
-  <si>
-    <t>ЛК-5</t>
-  </si>
-  <si>
-    <t>Армировка сеткой 50х50 яч.</t>
-  </si>
-  <si>
-    <t>м2</t>
+составом RC45) / ср. тольщина 30 мм</t>
+  </si>
+  <si>
+    <t>Лестницы (ср. тольщина 30 мм)</t>
+  </si>
+  <si>
+    <t>Лестницы, демонтаж тольщина слоя 30 мм</t>
   </si>
 </sst>
 </file>
@@ -167,7 +173,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -179,8 +185,25 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -189,56 +212,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -330,80 +303,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -710,224 +671,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="11.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="1.88671875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-    </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="3" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5">
+        <f>C12</f>
+        <v>161.20000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="5">
-        <f>C12</f>
-        <v>403.00000000000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>1</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="11">
-        <f>1.55*26*2</f>
-        <v>80.600000000000009</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+        <v>29.45</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="14">
-        <f>C7</f>
-        <v>80.600000000000009</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="11">
-        <f>C7</f>
-        <v>80.600000000000009</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+        <v>29.45</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="14">
-        <f>C7</f>
-        <v>80.600000000000009</v>
-      </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+        <v>40.300000000000004</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>5</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11">
-        <f>C7</f>
-        <v>80.600000000000009</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(C7:C11)</f>
-        <v>403.00000000000006</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+        <v>161.20000000000002</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:I12"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="D5:F12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -935,227 +852,202 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="1.88671875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="212" width="8.88671875" style="1"/>
+    <col min="213" max="213" width="7.77734375" style="1" customWidth="1"/>
+    <col min="214" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="3" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="B3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
         <f>D12</f>
-        <v>5.58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>2.0119500000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>1</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="11">
-        <f>24*1.55</f>
-        <v>37.200000000000003</v>
+        <v>13.26</v>
       </c>
       <c r="D7" s="11">
         <f>C7*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.39779999999999999</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>2</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="14">
-        <v>37.200000000000003</v>
+        <v>14.055</v>
       </c>
       <c r="D8" s="14">
         <f>C8*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.42164999999999997</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="11">
-        <v>37.200000000000003</v>
+        <v>7.6650000000000009</v>
       </c>
       <c r="D9" s="11">
         <f>C9*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.22995000000000002</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="14">
-        <v>37.200000000000003</v>
+        <v>18.134999999999998</v>
       </c>
       <c r="D10" s="14">
         <f>C10*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.54404999999999992</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>5</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11">
-        <v>37.200000000000003</v>
+        <v>13.950000000000001</v>
       </c>
       <c r="D11" s="11">
         <f>C11*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.41850000000000004</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(C7:C11)</f>
-        <v>186</v>
+        <v>67.064999999999998</v>
       </c>
       <c r="D12" s="11">
         <f>SUM(D7:D11)</f>
-        <v>5.58</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
+        <v>2.0119500000000001</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H12"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="E5:F12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1163,246 +1055,219 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="1.88671875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="15.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="3" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="F3" s="5">
         <f>D13</f>
-        <v>5.58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2.4714</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="B4" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="5">
         <f>C13</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>82.38000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>1</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="11">
-        <v>37.200000000000003</v>
+        <v>21.6</v>
       </c>
       <c r="D8" s="11">
         <f>C8*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>2</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="14">
-        <v>37.200000000000003</v>
+        <v>14.055</v>
       </c>
       <c r="D9" s="14">
         <f>C9*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.42164999999999997</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="11">
-        <v>37.200000000000003</v>
+        <v>14.64</v>
       </c>
       <c r="D10" s="11">
         <f>C10*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.43919999999999998</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="14">
-        <v>37.200000000000003</v>
+        <v>18.134999999999998</v>
       </c>
       <c r="D11" s="14">
         <f>C11*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.54404999999999992</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>3</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="11">
-        <v>37.200000000000003</v>
+        <v>13.950000000000001</v>
       </c>
       <c r="D12" s="11">
         <f>C12*0.03</f>
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+        <v>0.41850000000000004</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(C8:C12)</f>
-        <v>186</v>
+        <v>82.38000000000001</v>
       </c>
       <c r="D13" s="11">
         <f>SUM(D8:D12)</f>
-        <v>5.58</v>
-      </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+        <v>2.4714</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:H13"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="E6:F13"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
